--- a/Parameter Exchange.xlsx
+++ b/Parameter Exchange.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
-  <workbookPr filterPrivacy="true" autoCompressPictures="false" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE278C5B-C410-4FF3-A913-5C7DB98BB808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="1" autoCompressPictures="0" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56D107C-7721-4D1C-8C52-40C16289E77C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Report!$A$2:$H$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Report!$A$2:$H$141</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="true" concurrentCalc="false"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2706" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="417">
   <si>
     <t>CSS</t>
   </si>
@@ -1116,9 +1116,6 @@
     <t>_2022x_68f01a1_1778759565453_992577_20256</t>
   </si>
   <si>
-    <t>10.700000000000001</t>
-  </si>
-  <si>
     <t>Telcordia Issue 4, Miscellaneous, Battery</t>
   </si>
   <si>
@@ -1260,7 +1257,7 @@
     <t>GPS_Failure_Rate</t>
   </si>
   <si>
-    <t>0.027556</t>
+    <t>IMU_Failure_Rate</t>
   </si>
   <si>
     <r>
@@ -1269,7 +1266,6 @@
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>Element ID</t>
     </r>
@@ -1281,7 +1277,6 @@
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>Owner</t>
     </r>
@@ -1293,7 +1288,6 @@
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>Name</t>
     </r>
@@ -1305,7 +1299,6 @@
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>Type</t>
     </r>
@@ -1317,7 +1310,6 @@
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>Default Value</t>
     </r>
@@ -1329,7 +1321,6 @@
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>Lower Value</t>
     </r>
@@ -1341,105 +1332,9 @@
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>Upper Value</t>
     </r>
-  </si>
-  <si>
-    <t>IMU_Failure_Rate</t>
-  </si>
-  <si>
-    <t>0.025609</t>
-  </si>
-  <si>
-    <t>0.013766</t>
-  </si>
-  <si>
-    <t>0.010323</t>
-  </si>
-  <si>
-    <t>0.010000</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <color rgb="FFFFFF"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Element ID</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <color rgb="FFFFFF"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Owner</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <color rgb="FFFFFF"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Name</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <color rgb="FFFFFF"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Type</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <color rgb="FFFFFF"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Default Value</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <color rgb="FFFFFF"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Lower Value</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <color rgb="FFFFFF"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Upper Value</t>
-    </r>
-  </si>
-  <si>
-    <t>0.7227829891521151</t>
   </si>
   <si>
     <t>69.9442520917341</t>
@@ -1449,8 +1344,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1461,7 +1355,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="0" rgb="FFFFFF"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1482,58 +1376,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <sz val="11"/>
-      <b val="true"/>
-      <color rgb="FFFFFF"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-      <b val="true"/>
-      <color rgb="FFFFFF"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-      <b val="true"/>
-      <color rgb="FFFFFF"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-      <b val="true"/>
-      <color rgb="FFFFFF"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-      <b val="true"/>
-      <color rgb="FFFFFF"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-      <b val="true"/>
-      <color rgb="FFFFFF"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-      <b val="true"/>
-      <color rgb="FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1545,12 +1396,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.49995422223579"/>
+        <fgColor theme="0" tint="-0.49995422223578601"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1560,16 +1411,16 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="true"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color auto="true"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color auto="true"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color auto="true"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1578,40 +1429,35 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color auto="true"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
-    <border/>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
-      <alignment vertical="top" wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
-      <alignment horizontal="left" vertical="top" wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
-      <alignment horizontal="left" vertical="top" wrapText="true"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1918,13 +1764,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J141"/>
-  <sheetFormatPr defaultColWidth="21.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="21.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="40.28515625"/>
-    <col min="5" max="5" customWidth="true" width="59.140625"/>
+    <col min="1" max="1" width="40.26953125" customWidth="1"/>
+    <col min="5" max="5" width="59.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="true" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1936,146 +1782,146 @@
       <c r="G1" s="6"/>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="7" t="n">
-        <v>200.0</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H3" s="0"/>
-    </row>
-    <row r="4" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="E3" s="2">
+        <v>200</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H3"/>
+    </row>
+    <row r="4" spans="1:10" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E4" s="7" t="n">
-        <v>520.0</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H4" s="0"/>
-    </row>
-    <row r="5" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="E4" s="2">
+        <v>520</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H4"/>
+    </row>
+    <row r="5" spans="1:10" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="2">
         <v>1.4</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="F5" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H6" s="0"/>
+      <c r="F6" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H6"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G7" s="7" t="s">
+      <c r="F7" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H7" s="5" t="s">
@@ -2083,3312 +1929,3312 @@
       </c>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="2">
         <v>22.2</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H8" s="0"/>
-    </row>
-    <row r="9" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="F8" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H8"/>
+    </row>
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="E9" s="7" t="n">
-        <v>180.0</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G9" s="7" t="s">
+      <c r="E9" s="2">
+        <v>180</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="E10" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="11" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:10" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E11" s="7" t="n">
-        <v>0.099107</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H11" s="0"/>
-    </row>
-    <row r="12" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="E11" s="2">
+        <v>9.9107000000000001E-2</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H11"/>
+    </row>
+    <row r="12" spans="1:10" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E12" s="7" t="n">
-        <v>1340.0</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="13" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="E12" s="2">
+        <v>1340</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="2">
         <v>0.49</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H13" s="0"/>
-    </row>
-    <row r="14" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="F13" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H13"/>
+    </row>
+    <row r="14" spans="1:10" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E14" s="7" t="n">
-        <v>1200.0</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H14" s="0"/>
-    </row>
-    <row r="15" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+      <c r="E14" s="2">
+        <v>1200</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H14"/>
+    </row>
+    <row r="15" spans="1:10" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E15" s="2">
         <v>0.65</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G15" s="7" t="s">
+      <c r="F15" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:10" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H16" s="0"/>
-    </row>
-    <row r="17" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="F16" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H16"/>
+    </row>
+    <row r="17" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H17" s="0"/>
-    </row>
-    <row r="18" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="E17" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H17"/>
+    </row>
+    <row r="18" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E18" s="7" t="n">
-        <v>0.027556</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H18" s="0"/>
-    </row>
-    <row r="19" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+      <c r="E18" s="2">
+        <v>2.7556000000000001E-2</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H18"/>
+    </row>
+    <row r="19" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E19" s="7" t="n">
-        <v>145.0</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G19" s="7" t="s">
+      <c r="E19" s="2">
+        <v>145</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E20" s="7" t="n">
+      <c r="E20" s="2">
         <v>0.12</v>
       </c>
-      <c r="F20" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H20" s="0"/>
-    </row>
-    <row r="21" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="F20" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H20"/>
+    </row>
+    <row r="21" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="F21" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G21" s="7" t="s">
+      <c r="F21" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="22" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G22" s="7" t="s">
+      <c r="F22" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E23" s="7" t="n">
-        <v>1.471549E-4</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H23" s="0"/>
-    </row>
-    <row r="24" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+      <c r="E23" s="2">
+        <v>1.4715489999999999E-4</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H23"/>
+    </row>
+    <row r="24" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E24" s="7" t="n">
-        <v>480.0</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G24" s="7" t="s">
+      <c r="E24" s="2">
+        <v>480</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="25" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E25" s="2">
         <v>0.18</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H25" s="0"/>
-    </row>
-    <row r="26" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+      <c r="F25" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H25"/>
+    </row>
+    <row r="26" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="F26" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H26" s="0"/>
-    </row>
-    <row r="27" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="F26" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H26"/>
+    </row>
+    <row r="27" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G27" s="7" t="s">
+      <c r="E27" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="28" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="B28" s="7" t="s">
+    <row r="28" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="D28" s="7" t="s">
+      <c r="C28" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E28" s="7" t="n">
-        <v>0.027556</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G28" s="7" t="s">
+      <c r="E28" s="2">
+        <v>2.7556000000000001E-2</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E29" s="7" t="n">
-        <v>2035.0</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G29" s="7" t="s">
+      <c r="E29" s="2">
+        <v>2035</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+    <row r="30" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="E30" s="2">
         <v>0.91</v>
       </c>
-      <c r="F30" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G30" s="7" t="s">
+      <c r="F30" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="31" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E31" s="7" t="n">
-        <v>1350.0</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G31" s="7" t="s">
+      <c r="E31" s="2">
+        <v>1350</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="32" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E32" s="7" t="n">
+      <c r="E32" s="2">
         <v>2.85</v>
       </c>
-      <c r="F32" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H32" s="0"/>
-    </row>
-    <row r="33" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+      <c r="F32" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H32"/>
+    </row>
+    <row r="33" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H33" s="0"/>
-    </row>
-    <row r="34" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+      <c r="F33" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H33"/>
+    </row>
+    <row r="34" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H34" s="0"/>
-    </row>
-    <row r="35" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+      <c r="E34" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H34"/>
+    </row>
+    <row r="35" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E35" s="7" t="n">
+      <c r="E35" s="2">
         <v>0.01</v>
       </c>
-      <c r="F35" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G35" s="7" t="s">
+      <c r="F35" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="36" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
+    <row r="36" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E36" s="7" t="n">
-        <v>145.0</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H36" s="0"/>
-    </row>
-    <row r="37" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
+      <c r="E36" s="2">
+        <v>145</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H36"/>
+    </row>
+    <row r="37" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E37" s="7" t="n">
+      <c r="E37" s="2">
         <v>0.05</v>
       </c>
-      <c r="F37" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G37" s="7" t="s">
+      <c r="F37" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
+    <row r="38" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="F38" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G38" s="7" t="s">
+      <c r="F38" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
+    <row r="39" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E39" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G39" s="7" t="s">
+      <c r="E39" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="B40" s="7" t="s">
+    <row r="40" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C40" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="D40" s="7" t="s">
+      <c r="C40" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E40" s="7" t="n">
-        <v>0.025609</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H40" s="0"/>
-    </row>
-    <row r="41" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
+      <c r="E40" s="2">
+        <v>2.5609E-2</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H40"/>
+    </row>
+    <row r="41" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E41" s="7" t="n">
-        <v>320.0</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H41" s="0"/>
-    </row>
-    <row r="42" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
+      <c r="E41" s="2">
+        <v>320</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H41"/>
+    </row>
+    <row r="42" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E42" s="7" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G42" s="7" t="s">
+      <c r="E42" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
+    <row r="43" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="E43" s="7" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G43" s="7" t="s">
+      <c r="E43" s="2">
+        <v>4</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="44" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
+    <row r="44" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E44" s="7" t="n">
+      <c r="E44" s="2">
         <v>0.17</v>
       </c>
-      <c r="F44" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G44" s="7" t="s">
+      <c r="F44" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="45" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
+    <row r="45" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E45" s="7" t="n">
+      <c r="E45" s="2">
         <v>0.62</v>
       </c>
-      <c r="F45" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G45" s="7" t="s">
+      <c r="F45" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
+    <row r="46" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E46" s="7" t="n">
+      <c r="E46" s="2">
         <v>0.09</v>
       </c>
-      <c r="F46" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G46" s="7" t="s">
+      <c r="F46" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
+    <row r="47" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D47" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E47" s="7" t="n">
+      <c r="E47" s="2">
         <v>0.95</v>
       </c>
-      <c r="F47" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H47" s="0"/>
-    </row>
-    <row r="48" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
+      <c r="F47" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H47"/>
+    </row>
+    <row r="48" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E48" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="F48" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H48" s="0"/>
-    </row>
-    <row r="49" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
+      <c r="F48" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H48"/>
+    </row>
+    <row r="49" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E49" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G49" s="7" t="s">
+      <c r="E49" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G49" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
+    <row r="50" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E50" s="7" t="n">
+      <c r="E50" s="2">
         <v>0.01</v>
       </c>
-      <c r="F50" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G50" s="7" t="s">
+      <c r="F50" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
+    <row r="51" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E51" s="7" t="n">
-        <v>210.0</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G51" s="7" t="s">
+      <c r="E51" s="2">
+        <v>210</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G51" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
+    <row r="52" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E52" s="7" t="n">
+      <c r="E52" s="2">
         <v>0.03</v>
       </c>
-      <c r="F52" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G52" s="7" t="s">
+      <c r="F52" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G52" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H52" s="5" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
+    <row r="53" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D53" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E53" s="7" t="s">
+      <c r="E53" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="F53" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H53" s="0"/>
-    </row>
-    <row r="54" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
+      <c r="F53" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H53"/>
+    </row>
+    <row r="54" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="D54" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E54" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H54" s="0"/>
-    </row>
-    <row r="55" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="B55" s="7" t="s">
+      <c r="E54" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H54"/>
+    </row>
+    <row r="55" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C55" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="D55" s="7" t="s">
+      <c r="C55" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E55" s="7" t="n">
-        <v>0.025609</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G55" s="7" t="s">
+      <c r="E55" s="2">
+        <v>2.5609E-2</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G55" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="56" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
+    <row r="56" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D56" s="7" t="s">
+      <c r="D56" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E56" s="7" t="n">
-        <v>260.0</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H56" s="0"/>
-    </row>
-    <row r="57" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
+      <c r="E56" s="2">
+        <v>260</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H56"/>
+    </row>
+    <row r="57" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D57" s="7" t="s">
+      <c r="D57" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E57" s="7" t="n">
+      <c r="E57" s="2">
         <v>0.42</v>
       </c>
-      <c r="F57" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H57" s="0"/>
-    </row>
-    <row r="58" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
+      <c r="F57" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H57"/>
+    </row>
+    <row r="58" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="D58" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E58" s="7" t="s">
+      <c r="E58" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="F58" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G58" s="7" t="s">
+      <c r="F58" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G58" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="59" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
+    <row r="59" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="D59" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E59" s="7" t="s">
+      <c r="E59" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F59" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G59" s="7" t="s">
+      <c r="F59" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G59" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A60" s="7" t="s">
+    <row r="60" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D60" s="7" t="s">
+      <c r="D60" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E60" s="7" t="n">
+      <c r="E60" s="2">
         <v>0.65</v>
       </c>
-      <c r="F60" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G60" s="7" t="s">
+      <c r="F60" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G60" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="61" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
+    <row r="61" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="D61" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E61" s="7" t="n">
+      <c r="E61" s="2">
         <v>0.52</v>
       </c>
-      <c r="F61" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G61" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H61" s="0"/>
-    </row>
-    <row r="62" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
+      <c r="F61" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H61"/>
+    </row>
+    <row r="62" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B62" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="D62" s="7" t="s">
+      <c r="D62" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E62" s="7" t="n">
-        <v>6.858593</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G62" s="7" t="s">
+      <c r="E62" s="2">
+        <v>6.8585929999999999</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G62" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="63" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
+    <row r="63" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D63" s="7" t="s">
+      <c r="D63" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E63" s="7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G63" s="7" t="s">
+      <c r="E63" s="2">
+        <v>2</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H63" s="5" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="64" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
+    <row r="64" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D64" s="7" t="s">
+      <c r="D64" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E64" s="7" t="n">
-        <v>410.0</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H64" s="0"/>
-    </row>
-    <row r="65" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
+      <c r="E64" s="2">
+        <v>410</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H64"/>
+    </row>
+    <row r="65" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B65" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="D65" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E65" s="7" t="n">
+      <c r="E65" s="2">
         <v>0.9</v>
       </c>
-      <c r="F65" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G65" s="7" t="s">
+      <c r="F65" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G65" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H65" s="5" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="66" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="s">
+    <row r="66" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="B66" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="D66" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E66" s="7" t="s">
+      <c r="E66" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="F66" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G66" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H66" s="0"/>
-    </row>
-    <row r="67" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
+      <c r="F66" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H66"/>
+    </row>
+    <row r="67" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C67" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="D67" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E67" s="7" t="s">
+      <c r="E67" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H67"/>
+    </row>
+    <row r="68" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="F67" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H67" s="0"/>
-    </row>
-    <row r="68" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
+      <c r="B68" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="D68" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E68" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H68"/>
+    </row>
+    <row r="69" spans="1:8" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C68" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E68" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G68" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H68" s="0"/>
-    </row>
-    <row r="69" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
+      <c r="C69" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B69" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="D69" s="7" t="s">
+      <c r="D69" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E69" s="7" t="n">
+      <c r="E69" s="2">
         <v>0.01</v>
       </c>
-      <c r="F69" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G69" s="7" t="s">
+      <c r="F69" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G69" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H69" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="70" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="s">
+    <row r="70" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="D70" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E70" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H70"/>
+    </row>
+    <row r="71" spans="1:8" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C70" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="D70" s="7" t="s">
+      <c r="C71" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E70" s="7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G70" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H70" s="0"/>
-    </row>
-    <row r="71" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E71" s="7" t="n">
+      <c r="E71" s="2">
         <v>0.35</v>
       </c>
-      <c r="F71" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G71" s="7" t="s">
+      <c r="F71" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G71" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="72" ht="30" x14ac:dyDescent="0.25">
-      <c r="A72" s="7" t="s">
+    <row r="72" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A72" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B72" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="C72" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D72" s="7" t="s">
+      <c r="D72" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E72" s="7" t="n">
+      <c r="E72" s="2">
         <v>0.32</v>
       </c>
-      <c r="F72" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="73" ht="30" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
+      <c r="F72" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A73" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B73" s="7" t="s">
+      <c r="B73" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="C73" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D73" s="7" t="s">
+      <c r="D73" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E73" s="7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F73" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G73" s="7" t="s">
+      <c r="E73" s="2">
+        <v>2</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G73" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H73" s="5" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="74" ht="30" x14ac:dyDescent="0.25">
-      <c r="A74" s="7" t="s">
+    <row r="74" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A74" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="B74" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="C74" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="D74" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E74" s="7" t="n">
+      <c r="E74" s="2">
         <v>0.34</v>
       </c>
-      <c r="F74" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G74" s="7" t="s">
+      <c r="F74" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H74" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="75" ht="30" x14ac:dyDescent="0.25">
-      <c r="A75" s="7" t="s">
+    <row r="75" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A75" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B75" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="C75" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="D75" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E75" s="7" t="n">
+      <c r="E75" s="2">
         <v>0.18</v>
       </c>
-      <c r="F75" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G75" s="7" t="s">
+      <c r="F75" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G75" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H75" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="76" ht="30" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
+    <row r="76" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A76" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D76" s="7" t="s">
+      <c r="D76" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="E76" s="7" t="n">
-        <v>18.0</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G76" s="7" t="s">
+      <c r="E76" s="2">
+        <v>18</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G76" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="77" ht="30" x14ac:dyDescent="0.25">
-      <c r="A77" s="7" t="s">
+    <row r="77" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A77" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="B77" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C77" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="D77" s="7" t="s">
+      <c r="D77" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E77" s="7" t="n">
+      <c r="E77" s="2">
         <v>0.03</v>
       </c>
-      <c r="F77" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G77" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="78" ht="30" x14ac:dyDescent="0.25">
-      <c r="A78" s="7" t="s">
+      <c r="F77" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A78" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="B78" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="C78" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="D78" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E78" s="7" t="n">
+      <c r="E78" s="2">
         <v>0.16</v>
       </c>
-      <c r="F78" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G78" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="79" ht="30" x14ac:dyDescent="0.25">
-      <c r="A79" s="7" t="s">
+      <c r="F78" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A79" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="B79" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="C79" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D79" s="7" t="s">
+      <c r="D79" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E79" s="7" t="n">
-        <v>75.0</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G79" s="7" t="s">
+      <c r="E79" s="2">
+        <v>75</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G79" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H79" s="5" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="80" ht="30" x14ac:dyDescent="0.25">
-      <c r="A80" s="7" t="s">
+    <row r="80" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A80" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="B80" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="C80" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D80" s="7" t="s">
+      <c r="D80" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E80" s="7" t="n">
+      <c r="E80" s="2">
         <v>0.09</v>
       </c>
-      <c r="F80" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G80" s="7" t="s">
+      <c r="F80" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G80" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H80" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="81" ht="30" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
+    <row r="81" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A81" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="B81" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C81" s="7" t="s">
+      <c r="C81" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D81" s="7" t="s">
+      <c r="D81" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E81" s="7" t="s">
+      <c r="E81" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="F81" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G81" s="7" t="s">
+      <c r="F81" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G81" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H81" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="82" ht="30" x14ac:dyDescent="0.25">
-      <c r="A82" s="7" t="s">
+    <row r="82" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A82" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="B82" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="C82" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D82" s="7" t="s">
+      <c r="D82" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E82" s="7" t="s">
+      <c r="E82" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F82" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G82" s="7" t="s">
+      <c r="F82" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G82" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H82" s="5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="83" ht="30" x14ac:dyDescent="0.25">
-      <c r="A83" s="7" t="s">
+    <row r="83" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A83" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B83" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="D83" s="7" t="s">
+      <c r="D83" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E83" s="7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G83" s="7" t="s">
+      <c r="E83" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G83" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H83" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="84" ht="30" x14ac:dyDescent="0.25">
-      <c r="A84" s="7" t="s">
+    <row r="84" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A84" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B84" s="7" t="s">
+      <c r="B84" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C84" s="7" t="s">
+      <c r="C84" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D84" s="7" t="s">
+      <c r="D84" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E84" s="7" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="85" ht="30" x14ac:dyDescent="0.25">
-      <c r="A85" s="7" t="s">
+      <c r="E84" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A85" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B85" s="7" t="s">
+      <c r="B85" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="C85" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D85" s="7" t="s">
+      <c r="D85" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E85" s="7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="86" ht="45" x14ac:dyDescent="0.25">
-      <c r="A86" s="7" t="s">
+      <c r="E85" s="2">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A86" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B86" s="7" t="s">
+      <c r="B86" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="C86" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D86" s="7" t="s">
+      <c r="D86" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E86" s="7" t="n">
+      <c r="E86" s="2">
         <v>0.8</v>
       </c>
-      <c r="F86" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G86" s="7" t="s">
+      <c r="F86" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G86" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="87" ht="30" x14ac:dyDescent="0.25">
-      <c r="A87" s="7" t="s">
+    <row r="87" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A87" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B87" s="7" t="s">
+      <c r="B87" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C87" s="7" t="s">
+      <c r="C87" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D87" s="7" t="s">
+      <c r="D87" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E87" s="7" t="n">
-        <v>340.0</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G87" s="7" t="s">
+      <c r="E87" s="2">
+        <v>340</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G87" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="88" ht="30" x14ac:dyDescent="0.25">
-      <c r="A88" s="7" t="s">
+    <row r="88" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A88" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B88" s="7" t="s">
+      <c r="B88" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C88" s="7" t="s">
+      <c r="C88" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D88" s="7" t="s">
+      <c r="D88" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E88" s="7" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F88" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G88" s="7" t="s">
+      <c r="E88" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G88" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="89" ht="30" x14ac:dyDescent="0.25">
-      <c r="A89" s="7" t="s">
+    <row r="89" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A89" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B89" s="7" t="s">
+      <c r="B89" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="C89" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D89" s="7" t="s">
+      <c r="D89" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E89" s="7" t="s">
+      <c r="E89" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="F89" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G89" s="7" t="s">
+      <c r="F89" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G89" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="90" ht="30" x14ac:dyDescent="0.25">
-      <c r="A90" s="7" t="s">
+    <row r="90" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A90" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B90" s="7" t="s">
+      <c r="B90" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C90" s="7" t="s">
+      <c r="C90" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D90" s="7" t="s">
+      <c r="D90" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E90" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G90" s="7" t="s">
+      <c r="E90" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G90" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="91" ht="30" x14ac:dyDescent="0.25">
-      <c r="A91" s="7" t="s">
+    <row r="91" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A91" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="B91" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="C91" s="7" t="s">
+      <c r="D91" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E91" s="2">
+        <v>2.5609E-2</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A92" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E92" s="2">
+        <v>95</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A93" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A94" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A95" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A96" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="D91" s="7" t="s">
+      <c r="B96" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E91" s="7" t="n">
-        <v>0.025609</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G91" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="92" ht="30" x14ac:dyDescent="0.25">
-      <c r="A92" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="B92" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D92" s="7" t="s">
+      <c r="E96" s="2">
+        <v>2.5609E-2</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A97" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E97" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A98" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E98" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A99" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E92" s="7" t="n">
-        <v>95.0</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G92" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="93" ht="30" x14ac:dyDescent="0.25">
-      <c r="A93" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="E93" s="7" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G93" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="94" ht="30" x14ac:dyDescent="0.25">
-      <c r="A94" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="95" ht="30" x14ac:dyDescent="0.25">
-      <c r="A95" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="B95" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="E95" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="96" ht="30" x14ac:dyDescent="0.25">
-      <c r="A96" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="D96" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="E96" s="7" t="n">
-        <v>0.025609</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G96" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="97" ht="30" x14ac:dyDescent="0.25">
-      <c r="A97" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="E97" s="7" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G97" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A98" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="E98" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="99" ht="30" x14ac:dyDescent="0.25">
-      <c r="A99" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B99" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="D99" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="E99" s="7" t="n">
-        <v>3325.0</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G99" s="7" t="s">
+      <c r="E99" s="2">
+        <v>3325</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G99" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="100" ht="30" x14ac:dyDescent="0.25">
-      <c r="A100" s="7" t="s">
+    <row r="100" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A100" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B100" s="7" t="s">
+      <c r="B100" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C100" s="7" t="s">
+      <c r="C100" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="D100" s="7" t="s">
+      <c r="D100" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E100" s="7" t="n">
+      <c r="E100" s="2">
         <v>6.82</v>
       </c>
-      <c r="F100" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G100" s="7" t="s">
+      <c r="F100" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G100" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="101" ht="30" x14ac:dyDescent="0.25">
-      <c r="A101" s="7" t="s">
+    <row r="101" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A101" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B101" s="7" t="s">
+      <c r="B101" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C101" s="7" t="s">
+      <c r="C101" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D101" s="7" t="s">
+      <c r="D101" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E101" s="7" t="n">
-        <v>125.0</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G101" s="7" t="s">
+      <c r="E101" s="2">
+        <v>125</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G101" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="102" ht="30" x14ac:dyDescent="0.25">
-      <c r="A102" s="7" t="s">
+    <row r="102" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A102" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B102" s="7" t="s">
+      <c r="B102" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C102" s="7" t="s">
+      <c r="C102" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D102" s="7" t="s">
+      <c r="D102" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E102" s="7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G102" s="7" t="s">
+      <c r="E102" s="2">
+        <v>2</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G102" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="103" ht="30" x14ac:dyDescent="0.25">
-      <c r="A103" s="7" t="s">
+    <row r="103" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A103" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B103" s="7" t="s">
+      <c r="B103" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C103" s="7" t="s">
+      <c r="C103" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D103" s="7" t="s">
+      <c r="D103" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E103" s="7" t="s">
+      <c r="E103" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="F103" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G103" s="7" t="s">
+      <c r="F103" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G103" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="104" ht="30" x14ac:dyDescent="0.25">
-      <c r="A104" s="7" t="s">
+    <row r="104" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A104" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B104" s="7" t="s">
+      <c r="B104" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C104" s="7" t="s">
+      <c r="C104" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D104" s="7" t="s">
+      <c r="D104" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E104" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="F104" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G104" s="7" t="s">
+      <c r="E104" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G104" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="105" ht="30" x14ac:dyDescent="0.25">
-      <c r="A105" s="7" t="s">
+    <row r="105" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A105" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B105" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="D105" s="7" t="s">
+      <c r="D105" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E105" s="7" t="n">
-        <v>0.013766</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G105" s="7" t="s">
+      <c r="E105" s="2">
+        <v>1.3766E-2</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G105" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="106" ht="30" x14ac:dyDescent="0.25">
-      <c r="A106" s="7" t="s">
+    <row r="106" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A106" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B106" s="7" t="s">
+      <c r="B106" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C106" s="7" t="s">
+      <c r="C106" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="D106" s="7" t="s">
+      <c r="D106" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="E106" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="F106" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G106" s="7" t="s">
+      <c r="E106" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G106" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="107" ht="30" x14ac:dyDescent="0.25">
-      <c r="A107" s="7" t="s">
+    <row r="107" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A107" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B107" s="7" t="s">
+      <c r="B107" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C107" s="7" t="s">
+      <c r="C107" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="D107" s="7" t="s">
+      <c r="D107" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E107" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G107" s="7" t="s">
+      <c r="E107" s="2">
+        <v>10.25</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G107" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H107" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="108" ht="30" x14ac:dyDescent="0.25">
-      <c r="A108" s="7" t="s">
+    <row r="108" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A108" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B108" s="7" t="s">
+      <c r="B108" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C108" s="7" t="s">
+      <c r="C108" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D108" s="7" t="s">
+      <c r="D108" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E108" s="7" t="n">
-        <v>92.0</v>
-      </c>
-      <c r="F108" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G108" s="7" t="s">
+      <c r="E108" s="2">
+        <v>92</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G108" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="109" ht="30" x14ac:dyDescent="0.25">
-      <c r="A109" s="7" t="s">
+    <row r="109" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A109" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="B109" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="D109" s="7" t="s">
+      <c r="D109" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E109" s="7" t="n">
-        <v>7700.0</v>
-      </c>
-      <c r="F109" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G109" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="110" ht="30" x14ac:dyDescent="0.25">
-      <c r="A110" s="7" t="s">
+      <c r="E109" s="2">
+        <v>7700</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A110" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B110" s="7" t="s">
+      <c r="B110" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C110" s="7" t="s">
+      <c r="C110" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D110" s="7" t="s">
+      <c r="D110" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E110" s="7" t="n">
+      <c r="E110" s="2">
         <v>0.26</v>
       </c>
-      <c r="F110" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G110" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="111" ht="30" x14ac:dyDescent="0.25">
-      <c r="A111" s="7" t="s">
+      <c r="F110" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A111" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="B111" s="7" t="s">
+      <c r="B111" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C111" s="7" t="s">
+      <c r="C111" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D111" s="7" t="s">
+      <c r="D111" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E111" s="7" t="n">
+      <c r="E111" s="2">
         <v>0.17</v>
       </c>
-      <c r="F111" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G111" s="7" t="s">
+      <c r="F111" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G111" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="112" ht="30" x14ac:dyDescent="0.25">
-      <c r="A112" s="7" t="s">
+    <row r="112" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A112" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B112" s="7" t="s">
+      <c r="B112" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C112" s="7" t="s">
+      <c r="C112" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D112" s="7" t="s">
+      <c r="D112" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="E112" s="7" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="F112" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G112" s="7" t="s">
+      <c r="E112" s="2">
+        <v>28</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G112" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="113" ht="30" x14ac:dyDescent="0.25">
-      <c r="A113" s="7" t="s">
+    <row r="113" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A113" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B113" s="7" t="s">
+      <c r="B113" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C113" s="7" t="s">
+      <c r="C113" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D113" s="7" t="s">
+      <c r="D113" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E113" s="7" t="n">
+      <c r="E113" s="2">
         <v>0.09</v>
       </c>
-      <c r="F113" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G113" s="7" t="s">
+      <c r="F113" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G113" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="114" ht="30" x14ac:dyDescent="0.25">
-      <c r="A114" s="7" t="s">
+    <row r="114" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A114" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="B114" s="7" t="s">
+      <c r="B114" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C114" s="7" t="s">
+      <c r="C114" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D114" s="7" t="s">
+      <c r="D114" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E114" s="7" t="n">
+      <c r="E114" s="2">
         <v>0.11</v>
       </c>
-      <c r="F114" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G114" s="7" t="s">
+      <c r="F114" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G114" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H114" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="115" ht="30" x14ac:dyDescent="0.25">
-      <c r="A115" s="7" t="s">
+    <row r="115" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A115" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B115" s="7" t="s">
+      <c r="B115" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C115" s="7" t="s">
+      <c r="C115" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D115" s="7" t="s">
+      <c r="D115" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E115" s="7" t="n">
-        <v>295.0</v>
-      </c>
-      <c r="F115" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G115" s="7" t="s">
+      <c r="E115" s="2">
+        <v>295</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G115" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="116" ht="30" x14ac:dyDescent="0.25">
-      <c r="A116" s="7" t="s">
+    <row r="116" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A116" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B116" s="7" t="s">
+      <c r="B116" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C116" s="7" t="s">
+      <c r="C116" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D116" s="7" t="s">
+      <c r="D116" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E116" s="7" t="n">
+      <c r="E116" s="2">
         <v>0.42</v>
       </c>
-      <c r="F116" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G116" s="7" t="s">
+      <c r="F116" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G116" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H116" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="117" x14ac:dyDescent="0.25">
-      <c r="A117" s="7" t="s">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A117" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="B117" s="7" t="s">
+      <c r="B117" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C117" s="7" t="s">
+      <c r="C117" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="D117" s="7" t="s">
+      <c r="D117" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E117" s="7" t="s">
+      <c r="E117" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="F117" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G117" s="7" t="s">
+      <c r="F117" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G117" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="118" ht="30" x14ac:dyDescent="0.25">
-      <c r="A118" s="7" t="s">
+    <row r="118" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A118" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B118" s="7" t="s">
+      <c r="B118" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C118" s="7" t="s">
+      <c r="C118" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D118" s="7" t="s">
+      <c r="D118" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E118" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="F118" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G118" s="7" t="s">
+      <c r="E118" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G118" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="119" ht="30" x14ac:dyDescent="0.25">
-      <c r="A119" s="7" t="s">
+    <row r="119" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A119" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C119" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="B119" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C119" s="7" t="s">
+      <c r="D119" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E119" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A120" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E120" s="2">
+        <v>950</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A121" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E121" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A122" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E122" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A123" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E123" s="2">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A124" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E124" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A125" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E125" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A126" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E126" s="2">
+        <v>2</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A127" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E127" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A128" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E128" s="2">
+        <v>3</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A129" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E129" s="2">
+        <v>0</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A130" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E130" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A131" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E131" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A132" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E132" s="2">
+        <v>0.36</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A133" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E133" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A134" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A135" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A136" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="D119" s="7" t="s">
+      <c r="B136" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D136" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E119" s="7" t="n">
+      <c r="E136" s="2">
         <v>0.01</v>
       </c>
-      <c r="F119" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G119" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="120" ht="30" x14ac:dyDescent="0.25">
-      <c r="A120" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="B120" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D120" s="7" t="s">
+      <c r="F136" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A137" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D137" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E120" s="7" t="n">
-        <v>950.0</v>
-      </c>
-      <c r="F120" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G120" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="121" ht="30" x14ac:dyDescent="0.25">
-      <c r="A121" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="B121" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C121" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="D121" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E121" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G121" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="122" ht="30" x14ac:dyDescent="0.25">
-      <c r="A122" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="B122" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C122" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="D122" s="7" t="s">
+      <c r="E137" s="2">
+        <v>780</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A138" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D138" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E122" s="7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F122" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G122" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="123" ht="30" x14ac:dyDescent="0.25">
-      <c r="A123" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="B123" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C123" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="D123" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E123" s="7" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F123" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G123" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="124" ht="30" x14ac:dyDescent="0.25">
-      <c r="A124" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="B124" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C124" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="D124" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E124" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F124" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G124" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="125" ht="30" x14ac:dyDescent="0.25">
-      <c r="A125" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="B125" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C125" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="D125" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="E125" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F125" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G125" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="126" ht="30" x14ac:dyDescent="0.25">
-      <c r="A126" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="B126" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C126" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="D126" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="E126" s="7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F126" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G126" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="127" ht="30" x14ac:dyDescent="0.25">
-      <c r="A127" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="B127" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C127" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="D127" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E127" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F127" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G127" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="128" ht="30" x14ac:dyDescent="0.25">
-      <c r="A128" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="B128" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C128" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="D128" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E128" s="7" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F128" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G128" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="129" ht="30" x14ac:dyDescent="0.25">
-      <c r="A129" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="B129" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C129" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="D129" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="E129" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F129" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G129" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="130" ht="30" x14ac:dyDescent="0.25">
-      <c r="A130" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="B130" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C130" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="D130" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E130" s="7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="F130" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G130" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="131" ht="30" x14ac:dyDescent="0.25">
-      <c r="A131" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="B131" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C131" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="D131" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E131" s="7" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="F131" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G131" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="132" ht="30" x14ac:dyDescent="0.25">
-      <c r="A132" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="B132" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C132" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="D132" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E132" s="7" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="F132" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G132" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="133" ht="30" x14ac:dyDescent="0.25">
-      <c r="A133" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="B133" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C133" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="D133" s="7" t="s">
+      <c r="E138" s="2">
+        <v>0.22</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A139" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A140" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A141" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D141" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E133" s="7" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F133" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G133" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="134" ht="30" x14ac:dyDescent="0.25">
-      <c r="A134" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="B134" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C134" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="D134" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="E134" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="F134" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G134" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="135" ht="30" x14ac:dyDescent="0.25">
-      <c r="A135" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="B135" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C135" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="D135" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="E135" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="F135" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G135" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="136" ht="30" x14ac:dyDescent="0.25">
-      <c r="A136" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="B136" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C136" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="D136" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="E136" s="7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F136" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G136" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="137" ht="30" x14ac:dyDescent="0.25">
-      <c r="A137" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="B137" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="C137" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="D137" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="E137" s="7" t="n">
-        <v>780.0</v>
-      </c>
-      <c r="F137" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G137" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="138" ht="30" x14ac:dyDescent="0.25">
-      <c r="A138" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="B138" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="C138" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="D138" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="E138" s="7" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="F138" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G138" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="139" ht="30" x14ac:dyDescent="0.25">
-      <c r="A139" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="B139" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="C139" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="D139" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="E139" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="F139" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G139" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="140" ht="30" x14ac:dyDescent="0.25">
-      <c r="A140" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="B140" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="C140" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="D140" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="E140" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="F140" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G140" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="141" ht="30" x14ac:dyDescent="0.25">
-      <c r="A141" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="B141" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="C141" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="D141" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="E141" s="7" t="n">
-        <v>0.010323</v>
-      </c>
-      <c r="F141" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G141" s="7" t="s">
+      <c r="E141" s="2">
+        <v>1.0323000000000001E-2</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G141" s="2" t="s">
         <v>232</v>
       </c>
     </row>

--- a/Parameter Exchange.xlsx
+++ b/Parameter Exchange.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="true" autoCompressPictures="false" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE278C5B-C410-4FF3-A913-5C7DB98BB808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56D107C-7721-4D1C-8C52-40C16289E77C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2705" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="945" uniqueCount="417">
   <si>
     <t>CSS</t>
   </si>
@@ -1116,9 +1116,6 @@
     <t>_2022x_68f01a1_1778759565453_992577_20256</t>
   </si>
   <si>
-    <t>10.700000000000001</t>
-  </si>
-  <si>
     <t>Telcordia Issue 4, Miscellaneous, Battery</t>
   </si>
   <si>
@@ -1260,7 +1257,7 @@
     <t>GPS_Failure_Rate</t>
   </si>
   <si>
-    <t>0.027556</t>
+    <t>IMU_Failure_Rate</t>
   </si>
   <si>
     <r>
@@ -1269,7 +1266,6 @@
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>Element ID</t>
     </r>
@@ -1281,7 +1277,6 @@
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>Owner</t>
     </r>
@@ -1293,7 +1288,6 @@
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>Name</t>
     </r>
@@ -1305,7 +1299,6 @@
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>Type</t>
     </r>
@@ -1317,7 +1310,6 @@
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>Default Value</t>
     </r>
@@ -1329,7 +1321,6 @@
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>Lower Value</t>
     </r>
@@ -1341,113 +1332,19 @@
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>Upper Value</t>
     </r>
   </si>
   <si>
-    <t>IMU_Failure_Rate</t>
-  </si>
-  <si>
-    <t>0.025609</t>
-  </si>
-  <si>
-    <t>0.013766</t>
-  </si>
-  <si>
-    <t>0.010323</t>
-  </si>
-  <si>
-    <t>0.010000</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <color rgb="FFFFFF"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Element ID</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <color rgb="FFFFFF"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Owner</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <color rgb="FFFFFF"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Name</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <color rgb="FFFFFF"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Type</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <color rgb="FFFFFF"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Default Value</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <color rgb="FFFFFF"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Lower Value</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <color rgb="FFFFFF"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Upper Value</t>
-    </r>
-  </si>
-  <si>
-    <t>0.7227829891521151</t>
+    <t>69.9442520917341</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="13" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1479,58 +1376,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <sz val="11"/>
-      <b val="true"/>
-      <color rgb="FFFFFF"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-      <b val="true"/>
-      <color rgb="FFFFFF"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-      <b val="true"/>
-      <color rgb="FFFFFF"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-      <b val="true"/>
-      <color rgb="FFFFFF"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-      <b val="true"/>
-      <color rgb="FFFFFF"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-      <b val="true"/>
-      <color rgb="FFFFFF"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-      <b val="true"/>
-      <color rgb="FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1583,9 +1437,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
@@ -1605,14 +1459,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
-      <alignment horizontal="left" vertical="top" wrapText="true"/>
-    </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{E23A8A3D-9EA7-4417-AD7C-D941388C039B}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1628,7 +1479,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
     <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
@@ -1745,7 +1596,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1766,9 +1617,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="16200000" scaled="true"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1789,7 +1640,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="16200000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1818,7 +1669,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -1827,7 +1678,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1836,7 +1687,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1859,7 +1710,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1885,7 +1736,7 @@
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1913,15 +1764,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J141"/>
-  <sheetFormatPr defaultColWidth="21.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultColWidth="21.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.28515625" customWidth="true"/>
-    <col min="5" max="5" width="59.140625" customWidth="true"/>
+    <col min="1" max="1" width="40.26953125" customWidth="true"/>
+    <col min="5" max="5" width="55.90625" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="true" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" ht="30" customHeight="true" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1933,146 +1784,146 @@
       <c r="G1" s="6"/>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="7" t="n">
-        <v>200.0</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G3" s="7" t="s">
+      <c r="E3" s="2">
+        <v>200</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H3"/>
     </row>
-    <row r="4" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E4" s="7" t="n">
-        <v>520.0</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="E4" s="2">
+        <v>520</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H4"/>
     </row>
-    <row r="5" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E5" s="7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="E5" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G6" s="7" t="s">
+      <c r="F6" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H6"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G7" s="7" t="s">
+      <c r="F7" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H7" s="5" t="s">
@@ -2080,3317 +1931,3317 @@
       </c>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="2">
         <v>22.2</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G8" s="7" t="s">
+      <c r="F8" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H8"/>
     </row>
-    <row r="9" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="E9" s="7" t="n">
-        <v>180.0</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G9" s="7" t="s">
+      <c r="E9" s="2">
+        <v>180</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="E10" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="11" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E11" s="7" t="n">
-        <v>0.099107</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G11" s="7" t="s">
+      <c r="E11" s="2">
+        <v>9.9107000000000001E-2</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H11"/>
     </row>
-    <row r="12" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E12" s="7" t="n">
-        <v>1340.0</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="13" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="E12" s="2">
+        <v>1340</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="2">
         <v>0.49</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G13" s="7" t="s">
+      <c r="F13" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H13"/>
     </row>
-    <row r="14" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E14" s="7" t="n">
-        <v>1200.0</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G14" s="7" t="s">
+      <c r="E14" s="2">
+        <v>1200</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H14"/>
     </row>
-    <row r="15" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E15" s="2">
         <v>0.65</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G15" s="7" t="s">
+      <c r="F15" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G16" s="7" t="s">
+      <c r="F16" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H16"/>
     </row>
-    <row r="17" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G17" s="7" t="s">
+      <c r="E17" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H17"/>
     </row>
-    <row r="18" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E18" s="7" t="n">
-        <v>0.027556</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G18" s="7" t="s">
+      <c r="E18" s="2">
+        <v>2.7556000000000001E-2</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H18"/>
     </row>
-    <row r="19" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E19" s="7" t="n">
-        <v>145.0</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G19" s="7" t="s">
+      <c r="E19" s="2">
+        <v>145</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E20" s="7" t="n">
+      <c r="E20" s="2">
         <v>0.12</v>
       </c>
-      <c r="F20" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G20" s="7" t="s">
+      <c r="F20" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H20"/>
     </row>
-    <row r="21" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="F21" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G21" s="7" t="s">
+      <c r="F21" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="22" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G22" s="7" t="s">
+      <c r="F22" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E23" s="7" t="n">
-        <v>1.471549E-4</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G23" s="7" t="s">
+      <c r="E23" s="2">
+        <v>1.4715489999999999E-4</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H23"/>
     </row>
-    <row r="24" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E24" s="7" t="n">
-        <v>480.0</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G24" s="7" t="s">
+      <c r="E24" s="2">
+        <v>480</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="25" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E25" s="2">
         <v>0.18</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G25" s="7" t="s">
+      <c r="F25" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H25"/>
     </row>
-    <row r="26" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="F26" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G26" s="7" t="s">
+      <c r="F26" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H26"/>
     </row>
-    <row r="27" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G27" s="7" t="s">
+      <c r="E27" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="28" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="B28" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="D28" s="7" t="s">
+      <c r="C28" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E28" s="7" t="n">
-        <v>0.027556</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G28" s="7" t="s">
+      <c r="E28" s="2">
+        <v>2.7556000000000001E-2</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E29" s="7" t="n">
-        <v>2035.0</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G29" s="7" t="s">
+      <c r="E29" s="2">
+        <v>2035</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="E30" s="2">
         <v>0.91</v>
       </c>
-      <c r="F30" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G30" s="7" t="s">
+      <c r="F30" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="31" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E31" s="7" t="n">
-        <v>1350.0</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G31" s="7" t="s">
+      <c r="E31" s="2">
+        <v>1350</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="32" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E32" s="7" t="n">
+      <c r="E32" s="2">
         <v>2.85</v>
       </c>
-      <c r="F32" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G32" s="7" t="s">
+      <c r="F32" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H32"/>
     </row>
-    <row r="33" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G33" s="7" t="s">
+      <c r="F33" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H33"/>
     </row>
-    <row r="34" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="34" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G34" s="7" t="s">
+      <c r="E34" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H34"/>
     </row>
-    <row r="35" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="35" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E35" s="7" t="n">
+      <c r="E35" s="2">
         <v>0.01</v>
       </c>
-      <c r="F35" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G35" s="7" t="s">
+      <c r="F35" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="36" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="36" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E36" s="7" t="n">
-        <v>145.0</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G36" s="7" t="s">
+      <c r="E36" s="2">
+        <v>145</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H36"/>
     </row>
-    <row r="37" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="37" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E37" s="7" t="n">
+      <c r="E37" s="2">
         <v>0.05</v>
       </c>
-      <c r="F37" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G37" s="7" t="s">
+      <c r="F37" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="38" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="F38" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G38" s="7" t="s">
+      <c r="F38" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="39" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E39" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G39" s="7" t="s">
+      <c r="E39" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="B40" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="40" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C40" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="D40" s="7" t="s">
+      <c r="C40" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E40" s="7" t="n">
-        <v>0.025609</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G40" s="7" t="s">
+      <c r="E40" s="2">
+        <v>2.5609E-2</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H40"/>
     </row>
-    <row r="41" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="41" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E41" s="7" t="n">
-        <v>320.0</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G41" s="7" t="s">
+      <c r="E41" s="2">
+        <v>320</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H41"/>
     </row>
-    <row r="42" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="42" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E42" s="7" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G42" s="7" t="s">
+      <c r="E42" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="43" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="E43" s="7" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G43" s="7" t="s">
+      <c r="E43" s="2">
+        <v>4</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="44" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="44" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E44" s="7" t="n">
+      <c r="E44" s="2">
         <v>0.17</v>
       </c>
-      <c r="F44" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G44" s="7" t="s">
+      <c r="F44" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="45" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="45" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E45" s="7" t="n">
+      <c r="E45" s="2">
         <v>0.62</v>
       </c>
-      <c r="F45" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G45" s="7" t="s">
+      <c r="F45" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="46" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E46" s="7" t="n">
+      <c r="E46" s="2">
         <v>0.09</v>
       </c>
-      <c r="F46" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G46" s="7" t="s">
+      <c r="F46" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="47" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D47" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E47" s="7" t="n">
+      <c r="E47" s="2">
         <v>0.95</v>
       </c>
-      <c r="F47" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G47" s="7" t="s">
+      <c r="F47" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H47"/>
     </row>
-    <row r="48" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="48" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E48" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="F48" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G48" s="7" t="s">
+      <c r="F48" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H48"/>
     </row>
-    <row r="49" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="49" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E49" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G49" s="7" t="s">
+      <c r="E49" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G49" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="50" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E50" s="7" t="n">
+      <c r="E50" s="2">
         <v>0.01</v>
       </c>
-      <c r="F50" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G50" s="7" t="s">
+      <c r="F50" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="51" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E51" s="7" t="n">
-        <v>210.0</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G51" s="7" t="s">
+      <c r="E51" s="2">
+        <v>210</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G51" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="52" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E52" s="7" t="n">
+      <c r="E52" s="2">
         <v>0.03</v>
       </c>
-      <c r="F52" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G52" s="7" t="s">
+      <c r="F52" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G52" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H52" s="5" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="53" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A53" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D53" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E53" s="7" t="s">
+      <c r="E53" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="F53" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G53" s="7" t="s">
+      <c r="F53" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G53" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H53"/>
     </row>
-    <row r="54" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="54" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="D54" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E54" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G54" s="7" t="s">
+      <c r="E54" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G54" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H54"/>
     </row>
-    <row r="55" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="B55" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="55" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C55" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="D55" s="7" t="s">
+      <c r="C55" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E55" s="7" t="n">
-        <v>0.025609</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G55" s="7" t="s">
+      <c r="E55" s="2">
+        <v>2.5609E-2</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G55" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="56" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="56" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A56" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D56" s="7" t="s">
+      <c r="D56" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E56" s="7" t="n">
-        <v>260.0</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G56" s="7" t="s">
+      <c r="E56" s="2">
+        <v>260</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G56" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H56"/>
     </row>
-    <row r="57" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="57" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A57" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D57" s="7" t="s">
+      <c r="D57" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E57" s="7" t="n">
+      <c r="E57" s="2">
         <v>0.42</v>
       </c>
-      <c r="F57" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G57" s="7" t="s">
+      <c r="F57" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H57"/>
     </row>
-    <row r="58" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="58" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="D58" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E58" s="7" t="s">
+      <c r="E58" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="F58" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G58" s="7" t="s">
+      <c r="F58" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G58" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="59" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="59" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A59" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="D59" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E59" s="7" t="s">
+      <c r="E59" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F59" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G59" s="7" t="s">
+      <c r="F59" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G59" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A60" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="60" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D60" s="7" t="s">
+      <c r="D60" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E60" s="7" t="n">
+      <c r="E60" s="2">
         <v>0.65</v>
       </c>
-      <c r="F60" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G60" s="7" t="s">
+      <c r="F60" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G60" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="61" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="61" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A61" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="D61" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E61" s="7" t="n">
+      <c r="E61" s="2">
         <v>0.52</v>
       </c>
-      <c r="F61" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G61" s="7" t="s">
+      <c r="F61" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H61"/>
     </row>
-    <row r="62" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="62" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A62" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B62" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="D62" s="7" t="s">
+      <c r="D62" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E62" s="7" t="n">
-        <v>6.858593</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G62" s="7" t="s">
+      <c r="E62" s="2">
+        <v>6.8585929999999999</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G62" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="63" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="63" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A63" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D63" s="7" t="s">
+      <c r="D63" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E63" s="7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G63" s="7" t="s">
+      <c r="E63" s="2">
+        <v>2</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H63" s="5" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="64" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="64" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A64" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D64" s="7" t="s">
+      <c r="D64" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E64" s="7" t="n">
-        <v>410.0</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G64" s="7" t="s">
+      <c r="E64" s="2">
+        <v>410</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G64" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H64"/>
     </row>
-    <row r="65" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="65" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A65" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B65" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="D65" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E65" s="7" t="n">
+      <c r="E65" s="2">
         <v>0.9</v>
       </c>
-      <c r="F65" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G65" s="7" t="s">
+      <c r="F65" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G65" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H65" s="5" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="66" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="66" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A66" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="B66" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="D66" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E66" s="7" t="s">
+      <c r="E66" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="F66" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G66" s="7" t="s">
+      <c r="F66" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G66" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H66"/>
     </row>
-    <row r="67" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="67" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A67" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C67" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="D67" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E67" s="7" t="s">
+      <c r="E67" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H67"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="68" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A68" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="F67" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H67"/>
-    </row>
-    <row r="68" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
+      <c r="B68" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="D68" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E68" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H68"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="69" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A69" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C68" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E68" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G68" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H68"/>
-    </row>
-    <row r="69" s="1" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
+      <c r="C69" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B69" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="D69" s="7" t="s">
+      <c r="D69" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E69" s="7" t="n">
+      <c r="E69" s="2">
         <v>0.01</v>
       </c>
-      <c r="F69" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G69" s="7" t="s">
+      <c r="F69" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G69" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H69" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="70" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="70" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A70" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="D70" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E70" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H70"/>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="71" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.35">
+      <c r="A71" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C70" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="D70" s="7" t="s">
+      <c r="C71" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E70" s="7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G70" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H70"/>
-    </row>
-    <row r="71" s="5" customFormat="true" ht="14.25" customHeight="true" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E71" s="7" t="n">
+      <c r="E71" s="2">
         <v>0.35</v>
       </c>
-      <c r="F71" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G71" s="7" t="s">
+      <c r="F71" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G71" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="72" ht="30" x14ac:dyDescent="0.25">
-      <c r="A72" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="72" ht="29" x14ac:dyDescent="0.35">
+      <c r="A72" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B72" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="C72" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D72" s="7" t="s">
+      <c r="D72" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E72" s="7" t="n">
+      <c r="E72" s="2">
         <v>0.32</v>
       </c>
-      <c r="F72" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="73" ht="30" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
+      <c r="F72" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="73" ht="29" x14ac:dyDescent="0.35">
+      <c r="A73" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B73" s="7" t="s">
+      <c r="B73" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="C73" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D73" s="7" t="s">
+      <c r="D73" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E73" s="7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F73" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G73" s="7" t="s">
+      <c r="E73" s="2">
+        <v>2</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G73" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H73" s="5" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="74" ht="30" x14ac:dyDescent="0.25">
-      <c r="A74" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="74" ht="29" x14ac:dyDescent="0.35">
+      <c r="A74" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="B74" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="C74" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="D74" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E74" s="7" t="n">
+      <c r="E74" s="2">
         <v>0.34</v>
       </c>
-      <c r="F74" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G74" s="7" t="s">
+      <c r="F74" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H74" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="75" ht="30" x14ac:dyDescent="0.25">
-      <c r="A75" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="75" ht="29" x14ac:dyDescent="0.35">
+      <c r="A75" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B75" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="C75" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="D75" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E75" s="7" t="n">
+      <c r="E75" s="2">
         <v>0.18</v>
       </c>
-      <c r="F75" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G75" s="7" t="s">
+      <c r="F75" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G75" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H75" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="76" ht="30" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="76" ht="29" x14ac:dyDescent="0.35">
+      <c r="A76" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D76" s="7" t="s">
+      <c r="D76" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="E76" s="7" t="n">
-        <v>18.0</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G76" s="7" t="s">
+      <c r="E76" s="2">
+        <v>18</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G76" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="77" ht="30" x14ac:dyDescent="0.25">
-      <c r="A77" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="77" ht="29" x14ac:dyDescent="0.35">
+      <c r="A77" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="B77" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C77" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="D77" s="7" t="s">
+      <c r="D77" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E77" s="7" t="n">
+      <c r="E77" s="2">
         <v>0.03</v>
       </c>
-      <c r="F77" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G77" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="78" ht="30" x14ac:dyDescent="0.25">
-      <c r="A78" s="7" t="s">
+      <c r="F77" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="78" ht="29" x14ac:dyDescent="0.35">
+      <c r="A78" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="B78" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="C78" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="D78" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E78" s="7" t="n">
+      <c r="E78" s="2">
         <v>0.16</v>
       </c>
-      <c r="F78" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G78" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="79" ht="30" x14ac:dyDescent="0.25">
-      <c r="A79" s="7" t="s">
+      <c r="F78" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="79" ht="29" x14ac:dyDescent="0.35">
+      <c r="A79" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="B79" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="C79" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D79" s="7" t="s">
+      <c r="D79" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E79" s="7" t="n">
-        <v>75.0</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G79" s="7" t="s">
+      <c r="E79" s="2">
+        <v>75</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G79" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H79" s="5" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="80" ht="30" x14ac:dyDescent="0.25">
-      <c r="A80" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="80" ht="29" x14ac:dyDescent="0.35">
+      <c r="A80" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="B80" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="C80" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D80" s="7" t="s">
+      <c r="D80" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E80" s="7" t="n">
+      <c r="E80" s="2">
         <v>0.09</v>
       </c>
-      <c r="F80" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G80" s="7" t="s">
+      <c r="F80" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G80" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H80" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="81" ht="30" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="81" ht="29" x14ac:dyDescent="0.35">
+      <c r="A81" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="B81" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C81" s="7" t="s">
+      <c r="C81" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D81" s="7" t="s">
+      <c r="D81" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E81" s="7" t="s">
+      <c r="E81" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="F81" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G81" s="7" t="s">
+      <c r="F81" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G81" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H81" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="82" ht="30" x14ac:dyDescent="0.25">
-      <c r="A82" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="82" ht="29" x14ac:dyDescent="0.35">
+      <c r="A82" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="B82" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="C82" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D82" s="7" t="s">
+      <c r="D82" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E82" s="7" t="s">
+      <c r="E82" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F82" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G82" s="7" t="s">
+      <c r="F82" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G82" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H82" s="5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="83" ht="30" x14ac:dyDescent="0.25">
-      <c r="A83" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="83" ht="29" x14ac:dyDescent="0.35">
+      <c r="A83" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B83" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="D83" s="7" t="s">
+      <c r="D83" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E83" s="7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G83" s="7" t="s">
+      <c r="E83" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G83" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H83" s="5" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="84" ht="30" x14ac:dyDescent="0.25">
-      <c r="A84" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="84" ht="29" x14ac:dyDescent="0.35">
+      <c r="A84" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B84" s="7" t="s">
+      <c r="B84" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C84" s="7" t="s">
+      <c r="C84" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D84" s="7" t="s">
+      <c r="D84" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E84" s="7" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="85" ht="30" x14ac:dyDescent="0.25">
-      <c r="A85" s="7" t="s">
+      <c r="E84" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="85" ht="29" x14ac:dyDescent="0.35">
+      <c r="A85" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B85" s="7" t="s">
+      <c r="B85" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="C85" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D85" s="7" t="s">
+      <c r="D85" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E85" s="7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="86" ht="45" x14ac:dyDescent="0.25">
-      <c r="A86" s="7" t="s">
+      <c r="E85" s="2">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="86" ht="29" x14ac:dyDescent="0.35">
+      <c r="A86" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B86" s="7" t="s">
+      <c r="B86" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="C86" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D86" s="7" t="s">
+      <c r="D86" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E86" s="7" t="n">
+      <c r="E86" s="2">
         <v>0.8</v>
       </c>
-      <c r="F86" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G86" s="7" t="s">
+      <c r="F86" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G86" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="87" ht="30" x14ac:dyDescent="0.25">
-      <c r="A87" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="87" ht="29" x14ac:dyDescent="0.35">
+      <c r="A87" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B87" s="7" t="s">
+      <c r="B87" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C87" s="7" t="s">
+      <c r="C87" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D87" s="7" t="s">
+      <c r="D87" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E87" s="7" t="n">
-        <v>340.0</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G87" s="7" t="s">
+      <c r="E87" s="2">
+        <v>340</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G87" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="88" ht="30" x14ac:dyDescent="0.25">
-      <c r="A88" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="88" ht="29" x14ac:dyDescent="0.35">
+      <c r="A88" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B88" s="7" t="s">
+      <c r="B88" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C88" s="7" t="s">
+      <c r="C88" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D88" s="7" t="s">
+      <c r="D88" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E88" s="7" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F88" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G88" s="7" t="s">
+      <c r="E88" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G88" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="89" ht="30" x14ac:dyDescent="0.25">
-      <c r="A89" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="89" ht="29" x14ac:dyDescent="0.35">
+      <c r="A89" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B89" s="7" t="s">
+      <c r="B89" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="C89" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D89" s="7" t="s">
+      <c r="D89" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E89" s="7" t="s">
+      <c r="E89" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="F89" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G89" s="7" t="s">
+      <c r="F89" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G89" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="90" ht="30" x14ac:dyDescent="0.25">
-      <c r="A90" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="90" ht="29" x14ac:dyDescent="0.35">
+      <c r="A90" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B90" s="7" t="s">
+      <c r="B90" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C90" s="7" t="s">
+      <c r="C90" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D90" s="7" t="s">
+      <c r="D90" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E90" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G90" s="7" t="s">
+      <c r="E90" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G90" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="91" ht="30" x14ac:dyDescent="0.25">
-      <c r="A91" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="91" ht="29" x14ac:dyDescent="0.35">
+      <c r="A91" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="B91" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="C91" s="7" t="s">
+      <c r="D91" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E91" s="2">
+        <v>2.5609E-2</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="92" ht="29" x14ac:dyDescent="0.35">
+      <c r="A92" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E92" s="2">
+        <v>95</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="93" ht="29" x14ac:dyDescent="0.35">
+      <c r="A93" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="94" ht="29" x14ac:dyDescent="0.35">
+      <c r="A94" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="95" ht="29" x14ac:dyDescent="0.35">
+      <c r="A95" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="96" ht="29" x14ac:dyDescent="0.35">
+      <c r="A96" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="D91" s="7" t="s">
+      <c r="B96" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E91" s="7" t="n">
-        <v>0.025609</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G91" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="92" ht="30" x14ac:dyDescent="0.25">
-      <c r="A92" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="B92" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D92" s="7" t="s">
+      <c r="E96" s="2">
+        <v>2.5609E-2</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="97" ht="29" x14ac:dyDescent="0.35">
+      <c r="A97" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E97" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="98" ht="29" x14ac:dyDescent="0.35">
+      <c r="A98" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E98" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="99" ht="29" x14ac:dyDescent="0.35">
+      <c r="A99" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E92" s="7" t="n">
-        <v>95.0</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G92" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="93" ht="30" x14ac:dyDescent="0.25">
-      <c r="A93" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="E93" s="7" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G93" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="94" ht="30" x14ac:dyDescent="0.25">
-      <c r="A94" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="95" ht="30" x14ac:dyDescent="0.25">
-      <c r="A95" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="B95" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="E95" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="96" ht="30" x14ac:dyDescent="0.25">
-      <c r="A96" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="D96" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="E96" s="7" t="n">
-        <v>0.025609</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G96" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="97" ht="30" x14ac:dyDescent="0.25">
-      <c r="A97" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="E97" s="7" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G97" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A98" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="E98" s="7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="99" ht="30" x14ac:dyDescent="0.25">
-      <c r="A99" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B99" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="D99" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="E99" s="7" t="n">
-        <v>3325.0</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G99" s="7" t="s">
+      <c r="E99" s="2">
+        <v>3325</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G99" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="100" ht="30" x14ac:dyDescent="0.25">
-      <c r="A100" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="100" ht="29" x14ac:dyDescent="0.35">
+      <c r="A100" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B100" s="7" t="s">
+      <c r="B100" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C100" s="7" t="s">
+      <c r="C100" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="D100" s="7" t="s">
+      <c r="D100" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E100" s="7" t="n">
+      <c r="E100" s="2">
         <v>6.82</v>
       </c>
-      <c r="F100" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G100" s="7" t="s">
+      <c r="F100" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G100" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="101" ht="30" x14ac:dyDescent="0.25">
-      <c r="A101" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="101" ht="29" x14ac:dyDescent="0.35">
+      <c r="A101" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B101" s="7" t="s">
+      <c r="B101" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C101" s="7" t="s">
+      <c r="C101" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D101" s="7" t="s">
+      <c r="D101" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E101" s="7" t="n">
-        <v>125.0</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G101" s="7" t="s">
+      <c r="E101" s="2">
+        <v>125</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G101" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="102" ht="30" x14ac:dyDescent="0.25">
-      <c r="A102" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="102" ht="29" x14ac:dyDescent="0.35">
+      <c r="A102" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B102" s="7" t="s">
+      <c r="B102" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C102" s="7" t="s">
+      <c r="C102" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D102" s="7" t="s">
+      <c r="D102" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E102" s="7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G102" s="7" t="s">
+      <c r="E102" s="2">
+        <v>2</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G102" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="103" ht="30" x14ac:dyDescent="0.25">
-      <c r="A103" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="103" ht="29" x14ac:dyDescent="0.35">
+      <c r="A103" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B103" s="7" t="s">
+      <c r="B103" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C103" s="7" t="s">
+      <c r="C103" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D103" s="7" t="s">
+      <c r="D103" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E103" s="7" t="s">
+      <c r="E103" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="F103" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G103" s="7" t="s">
+      <c r="F103" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G103" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="104" ht="30" x14ac:dyDescent="0.25">
-      <c r="A104" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="104" ht="29" x14ac:dyDescent="0.35">
+      <c r="A104" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B104" s="7" t="s">
+      <c r="B104" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C104" s="7" t="s">
+      <c r="C104" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D104" s="7" t="s">
+      <c r="D104" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E104" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="F104" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G104" s="7" t="s">
+      <c r="E104" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G104" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="105" ht="30" x14ac:dyDescent="0.25">
-      <c r="A105" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="105" ht="29" x14ac:dyDescent="0.35">
+      <c r="A105" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B105" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="D105" s="7" t="s">
+      <c r="D105" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E105" s="7" t="n">
-        <v>0.013766</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G105" s="7" t="s">
+      <c r="E105" s="2">
+        <v>1.3766E-2</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G105" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="106" ht="30" x14ac:dyDescent="0.25">
-      <c r="A106" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="106" ht="29" x14ac:dyDescent="0.35">
+      <c r="A106" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B106" s="7" t="s">
+      <c r="B106" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C106" s="7" t="s">
+      <c r="C106" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="D106" s="7" t="s">
+      <c r="D106" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="E106" s="7">
-        <v>69.9442520917341</v>
-      </c>
-      <c r="F106" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G106" s="7" t="s">
+      <c r="E106" s="2">
+        <v>73.014975354298031</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G106" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="107" ht="30" x14ac:dyDescent="0.25">
-      <c r="A107" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="107" ht="29" x14ac:dyDescent="0.35">
+      <c r="A107" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B107" s="7" t="s">
+      <c r="B107" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C107" s="7" t="s">
+      <c r="C107" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="D107" s="7" t="s">
+      <c r="D107" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E107" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G107" s="7" t="s">
+      <c r="E107" s="2">
+        <v>10.25</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G107" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H107" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="108" ht="30" x14ac:dyDescent="0.25">
-      <c r="A108" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="108" ht="29" x14ac:dyDescent="0.35">
+      <c r="A108" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B108" s="7" t="s">
+      <c r="B108" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C108" s="7" t="s">
+      <c r="C108" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D108" s="7" t="s">
+      <c r="D108" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E108" s="7" t="n">
-        <v>92.0</v>
-      </c>
-      <c r="F108" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G108" s="7" t="s">
+      <c r="E108" s="2">
+        <v>92</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G108" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="109" ht="30" x14ac:dyDescent="0.25">
-      <c r="A109" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="109" ht="29" x14ac:dyDescent="0.35">
+      <c r="A109" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="B109" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="D109" s="7" t="s">
+      <c r="D109" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E109" s="7" t="n">
-        <v>7700.0</v>
-      </c>
-      <c r="F109" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G109" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="110" ht="30" x14ac:dyDescent="0.25">
-      <c r="A110" s="7" t="s">
+      <c r="E109" s="2">
+        <v>7700</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="110" ht="29" x14ac:dyDescent="0.35">
+      <c r="A110" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B110" s="7" t="s">
+      <c r="B110" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C110" s="7" t="s">
+      <c r="C110" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D110" s="7" t="s">
+      <c r="D110" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E110" s="7" t="n">
+      <c r="E110" s="2">
         <v>0.26</v>
       </c>
-      <c r="F110" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G110" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="111" ht="30" x14ac:dyDescent="0.25">
-      <c r="A111" s="7" t="s">
+      <c r="F110" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="111" ht="29" x14ac:dyDescent="0.35">
+      <c r="A111" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="B111" s="7" t="s">
+      <c r="B111" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C111" s="7" t="s">
+      <c r="C111" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D111" s="7" t="s">
+      <c r="D111" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E111" s="7" t="n">
+      <c r="E111" s="2">
         <v>0.17</v>
       </c>
-      <c r="F111" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G111" s="7" t="s">
+      <c r="F111" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G111" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="112" ht="30" x14ac:dyDescent="0.25">
-      <c r="A112" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="112" ht="29" x14ac:dyDescent="0.35">
+      <c r="A112" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B112" s="7" t="s">
+      <c r="B112" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C112" s="7" t="s">
+      <c r="C112" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D112" s="7" t="s">
+      <c r="D112" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="E112" s="7" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="F112" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G112" s="7" t="s">
+      <c r="E112" s="2">
+        <v>28</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G112" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="113" ht="30" x14ac:dyDescent="0.25">
-      <c r="A113" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="113" ht="29" x14ac:dyDescent="0.35">
+      <c r="A113" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B113" s="7" t="s">
+      <c r="B113" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C113" s="7" t="s">
+      <c r="C113" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D113" s="7" t="s">
+      <c r="D113" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E113" s="7" t="n">
+      <c r="E113" s="2">
         <v>0.09</v>
       </c>
-      <c r="F113" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G113" s="7" t="s">
+      <c r="F113" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G113" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="114" ht="30" x14ac:dyDescent="0.25">
-      <c r="A114" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="114" ht="29" x14ac:dyDescent="0.35">
+      <c r="A114" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="B114" s="7" t="s">
+      <c r="B114" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C114" s="7" t="s">
+      <c r="C114" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D114" s="7" t="s">
+      <c r="D114" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E114" s="7" t="n">
+      <c r="E114" s="2">
         <v>0.11</v>
       </c>
-      <c r="F114" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G114" s="7" t="s">
+      <c r="F114" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G114" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H114" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="115" ht="30" x14ac:dyDescent="0.25">
-      <c r="A115" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="115" ht="29" x14ac:dyDescent="0.35">
+      <c r="A115" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B115" s="7" t="s">
+      <c r="B115" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C115" s="7" t="s">
+      <c r="C115" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D115" s="7" t="s">
+      <c r="D115" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E115" s="7" t="n">
-        <v>295.0</v>
-      </c>
-      <c r="F115" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G115" s="7" t="s">
+      <c r="E115" s="2">
+        <v>295</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G115" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="116" ht="30" x14ac:dyDescent="0.25">
-      <c r="A116" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="116" ht="29" x14ac:dyDescent="0.35">
+      <c r="A116" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B116" s="7" t="s">
+      <c r="B116" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C116" s="7" t="s">
+      <c r="C116" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D116" s="7" t="s">
+      <c r="D116" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E116" s="7" t="n">
+      <c r="E116" s="2">
         <v>0.42</v>
       </c>
-      <c r="F116" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G116" s="7" t="s">
+      <c r="F116" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G116" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H116" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="117" x14ac:dyDescent="0.25">
-      <c r="A117" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="117" x14ac:dyDescent="0.35">
+      <c r="A117" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="B117" s="7" t="s">
+      <c r="B117" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C117" s="7" t="s">
+      <c r="C117" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="D117" s="7" t="s">
+      <c r="D117" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E117" s="7" t="s">
+      <c r="E117" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="F117" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G117" s="7" t="s">
+      <c r="F117" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G117" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="118" ht="30" x14ac:dyDescent="0.25">
-      <c r="A118" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="118" ht="29" x14ac:dyDescent="0.35">
+      <c r="A118" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B118" s="7" t="s">
+      <c r="B118" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C118" s="7" t="s">
+      <c r="C118" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D118" s="7" t="s">
+      <c r="D118" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E118" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="F118" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G118" s="7" t="s">
+      <c r="E118" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G118" s="2" t="s">
         <v>232</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="119" ht="30" x14ac:dyDescent="0.25">
-      <c r="A119" s="7" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="119" ht="29" x14ac:dyDescent="0.35">
+      <c r="A119" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C119" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="B119" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C119" s="7" t="s">
+      <c r="D119" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E119" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="120" ht="29" x14ac:dyDescent="0.35">
+      <c r="A120" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E120" s="2">
+        <v>950</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="121" ht="29" x14ac:dyDescent="0.35">
+      <c r="A121" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E121" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="122" ht="29" x14ac:dyDescent="0.35">
+      <c r="A122" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E122" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="123" ht="29" x14ac:dyDescent="0.35">
+      <c r="A123" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E123" s="2">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="124" ht="29" x14ac:dyDescent="0.35">
+      <c r="A124" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E124" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="125" ht="29" x14ac:dyDescent="0.35">
+      <c r="A125" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E125" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="126" ht="29" x14ac:dyDescent="0.35">
+      <c r="A126" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E126" s="2">
+        <v>2</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="127" ht="29" x14ac:dyDescent="0.35">
+      <c r="A127" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E127" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="128" ht="29" x14ac:dyDescent="0.35">
+      <c r="A128" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E128" s="2">
+        <v>3</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="129" ht="29" x14ac:dyDescent="0.35">
+      <c r="A129" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E129" s="2">
+        <v>0</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="130" ht="29" x14ac:dyDescent="0.35">
+      <c r="A130" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E130" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="131" ht="29" x14ac:dyDescent="0.35">
+      <c r="A131" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E131" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="132" ht="29" x14ac:dyDescent="0.35">
+      <c r="A132" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E132" s="2">
+        <v>0.36</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="133" ht="29" x14ac:dyDescent="0.35">
+      <c r="A133" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E133" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="134" ht="29" x14ac:dyDescent="0.35">
+      <c r="A134" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="135" ht="29" x14ac:dyDescent="0.35">
+      <c r="A135" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="136" ht="29" x14ac:dyDescent="0.35">
+      <c r="A136" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="D119" s="7" t="s">
+      <c r="B136" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D136" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E119" s="7" t="n">
+      <c r="E136" s="2">
         <v>0.01</v>
       </c>
-      <c r="F119" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G119" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="120" ht="30" x14ac:dyDescent="0.25">
-      <c r="A120" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="B120" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D120" s="7" t="s">
+      <c r="F136" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="137" ht="29" x14ac:dyDescent="0.35">
+      <c r="A137" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D137" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E120" s="7" t="n">
-        <v>950.0</v>
-      </c>
-      <c r="F120" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G120" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="121" ht="30" x14ac:dyDescent="0.25">
-      <c r="A121" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="B121" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C121" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="D121" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E121" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G121" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="122" ht="30" x14ac:dyDescent="0.25">
-      <c r="A122" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="B122" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C122" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="D122" s="7" t="s">
+      <c r="E137" s="2">
+        <v>780</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="138" ht="29" x14ac:dyDescent="0.35">
+      <c r="A138" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D138" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E122" s="7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F122" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G122" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="123" ht="30" x14ac:dyDescent="0.25">
-      <c r="A123" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="B123" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C123" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="D123" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E123" s="7" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F123" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G123" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="124" ht="30" x14ac:dyDescent="0.25">
-      <c r="A124" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="B124" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C124" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="D124" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E124" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F124" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G124" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="125" ht="30" x14ac:dyDescent="0.25">
-      <c r="A125" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="B125" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C125" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="D125" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="E125" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F125" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G125" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="126" ht="30" x14ac:dyDescent="0.25">
-      <c r="A126" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="B126" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C126" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="D126" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="E126" s="7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F126" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G126" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="127" ht="30" x14ac:dyDescent="0.25">
-      <c r="A127" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="B127" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C127" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="D127" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E127" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F127" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G127" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="128" ht="30" x14ac:dyDescent="0.25">
-      <c r="A128" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="B128" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C128" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="D128" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E128" s="7" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F128" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G128" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="129" ht="30" x14ac:dyDescent="0.25">
-      <c r="A129" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="B129" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C129" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="D129" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="E129" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F129" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G129" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="130" ht="30" x14ac:dyDescent="0.25">
-      <c r="A130" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="B130" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C130" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="D130" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E130" s="7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="F130" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G130" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="131" ht="30" x14ac:dyDescent="0.25">
-      <c r="A131" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="B131" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C131" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="D131" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E131" s="7" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="F131" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G131" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="132" ht="30" x14ac:dyDescent="0.25">
-      <c r="A132" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="B132" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C132" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="D132" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E132" s="7" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="F132" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G132" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="133" ht="30" x14ac:dyDescent="0.25">
-      <c r="A133" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="B133" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C133" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="D133" s="7" t="s">
+      <c r="E138" s="2">
+        <v>0.22</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="139" ht="29" x14ac:dyDescent="0.35">
+      <c r="A139" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="140" ht="29" x14ac:dyDescent="0.35">
+      <c r="A140" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="141" ht="29" x14ac:dyDescent="0.35">
+      <c r="A141" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D141" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E133" s="7" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F133" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G133" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="134" ht="30" x14ac:dyDescent="0.25">
-      <c r="A134" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="B134" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C134" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="D134" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="E134" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="F134" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G134" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="135" ht="30" x14ac:dyDescent="0.25">
-      <c r="A135" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="B135" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C135" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="D135" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="E135" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="F135" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G135" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="136" ht="30" x14ac:dyDescent="0.25">
-      <c r="A136" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="B136" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C136" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="D136" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="E136" s="7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F136" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G136" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="137" ht="30" x14ac:dyDescent="0.25">
-      <c r="A137" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="B137" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="C137" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="D137" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="E137" s="7" t="n">
-        <v>780.0</v>
-      </c>
-      <c r="F137" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G137" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="138" ht="30" x14ac:dyDescent="0.25">
-      <c r="A138" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="B138" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="C138" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="D138" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="E138" s="7" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="F138" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G138" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="139" ht="30" x14ac:dyDescent="0.25">
-      <c r="A139" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="B139" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="C139" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="D139" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="E139" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="F139" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G139" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="140" ht="30" x14ac:dyDescent="0.25">
-      <c r="A140" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="B140" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="C140" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="D140" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="E140" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="F140" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G140" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="141" ht="30" x14ac:dyDescent="0.25">
-      <c r="A141" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="B141" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="C141" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="D141" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="E141" s="7" t="n">
-        <v>0.010323</v>
-      </c>
-      <c r="F141" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="G141" s="7" t="s">
+      <c r="E141" s="2">
+        <v>1.0323000000000001E-2</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G141" s="2" t="s">
         <v>232</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H141" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:H141"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
